--- a/源数据/projList.xlsx
+++ b/源数据/projList.xlsx
@@ -4,12 +4,10 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27020" windowHeight="13000"/>
+    <workbookView windowWidth="18270" windowHeight="7600"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -29,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="48">
   <si>
     <t>项目名称</t>
   </si>
@@ -173,15 +171,6 @@
   </si>
   <si>
     <t>https://oa.epoint.com.cn/epointprojectm/projectmanage/mission/projectmission/projectmissionlist?ProjectGuid=68aafcc9-690a-4baa-9493-7e2f9b134106</t>
-  </si>
-  <si>
-    <t>浙江云端保网络科技公司电子保函合作项目</t>
-  </si>
-  <si>
-    <t>泰顺县小额工程阳光交易系统建设项目</t>
-  </si>
-  <si>
-    <t>平阳县限额以下SaaS化平台建设项目</t>
   </si>
 </sst>
 </file>
@@ -808,10 +797,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1126,12 +1115,12 @@
   <dimension ref="A1:B48"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="1" width="72.5454545454545" style="2" customWidth="1"/>
-    <col min="2" max="2" width="57.8181818181818" style="2" customWidth="1"/>
+    <col min="1" max="1" width="72.5454545454545" style="1" customWidth="1"/>
+    <col min="2" max="2" width="57.8181818181818" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
@@ -1139,7 +1128,7 @@
       </c>
     </row>
     <row r="2" spans="1:2">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B2" t="s">
@@ -1147,7 +1136,7 @@
       </c>
     </row>
     <row r="3" spans="1:2">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B3" t="s">
@@ -1155,7 +1144,7 @@
       </c>
     </row>
     <row r="4" spans="1:2">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B4" t="s">
@@ -1163,7 +1152,7 @@
       </c>
     </row>
     <row r="5" spans="1:2">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B5" t="s">
@@ -1171,7 +1160,7 @@
       </c>
     </row>
     <row r="6" spans="1:2">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B6" t="s">
@@ -1179,7 +1168,7 @@
       </c>
     </row>
     <row r="7" spans="1:2">
-      <c r="A7" s="1" t="s">
+      <c r="A7" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B7" t="s">
@@ -1187,7 +1176,7 @@
       </c>
     </row>
     <row r="8" spans="1:2">
-      <c r="A8" s="1" t="s">
+      <c r="A8" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B8" t="s">
@@ -1195,7 +1184,7 @@
       </c>
     </row>
     <row r="9" spans="1:2">
-      <c r="A9" s="1" t="s">
+      <c r="A9" s="2" t="s">
         <v>16</v>
       </c>
       <c r="B9" t="s">
@@ -1203,7 +1192,7 @@
       </c>
     </row>
     <row r="10" spans="1:2">
-      <c r="A10" s="1" t="s">
+      <c r="A10" s="2" t="s">
         <v>18</v>
       </c>
       <c r="B10" t="s">
@@ -1211,7 +1200,7 @@
       </c>
     </row>
     <row r="11" spans="1:2">
-      <c r="A11" s="1" t="s">
+      <c r="A11" s="2" t="s">
         <v>20</v>
       </c>
       <c r="B11" t="s">
@@ -1219,7 +1208,7 @@
       </c>
     </row>
     <row r="12" spans="1:2">
-      <c r="A12" s="1" t="s">
+      <c r="A12" s="2" t="s">
         <v>22</v>
       </c>
       <c r="B12" t="s">
@@ -1227,7 +1216,7 @@
       </c>
     </row>
     <row r="13" spans="1:2">
-      <c r="A13" s="1" t="s">
+      <c r="A13" s="2" t="s">
         <v>24</v>
       </c>
       <c r="B13" t="s">
@@ -1235,7 +1224,7 @@
       </c>
     </row>
     <row r="14" spans="1:2">
-      <c r="A14" s="1" t="s">
+      <c r="A14" s="2" t="s">
         <v>26</v>
       </c>
       <c r="B14" t="s">
@@ -1243,7 +1232,7 @@
       </c>
     </row>
     <row r="15" spans="1:2">
-      <c r="A15" s="1" t="s">
+      <c r="A15" s="2" t="s">
         <v>28</v>
       </c>
       <c r="B15" t="s">
@@ -1251,7 +1240,7 @@
       </c>
     </row>
     <row r="16" spans="1:2">
-      <c r="A16" s="1" t="s">
+      <c r="A16" s="2" t="s">
         <v>30</v>
       </c>
       <c r="B16" t="s">
@@ -1259,7 +1248,7 @@
       </c>
     </row>
     <row r="17" spans="1:2">
-      <c r="A17" s="1" t="s">
+      <c r="A17" s="2" t="s">
         <v>32</v>
       </c>
       <c r="B17" t="s">
@@ -1267,7 +1256,7 @@
       </c>
     </row>
     <row r="18" spans="1:2">
-      <c r="A18" s="1" t="s">
+      <c r="A18" s="2" t="s">
         <v>34</v>
       </c>
       <c r="B18" t="s">
@@ -1275,19 +1264,19 @@
       </c>
     </row>
     <row r="19" spans="1:2">
-      <c r="A19" s="1" t="s">
+      <c r="A19" s="2" t="s">
         <v>36</v>
       </c>
       <c r="B19"/>
     </row>
     <row r="20" spans="1:2">
-      <c r="A20" s="1" t="s">
+      <c r="A20" s="2" t="s">
         <v>37</v>
       </c>
       <c r="B20"/>
     </row>
     <row r="21" spans="1:2">
-      <c r="A21" s="1" t="s">
+      <c r="A21" s="2" t="s">
         <v>38</v>
       </c>
       <c r="B21" t="s">
@@ -1295,7 +1284,7 @@
       </c>
     </row>
     <row r="22" spans="1:2">
-      <c r="A22" s="1" t="s">
+      <c r="A22" s="2" t="s">
         <v>40</v>
       </c>
       <c r="B22" t="s">
@@ -1303,7 +1292,7 @@
       </c>
     </row>
     <row r="23" spans="1:2">
-      <c r="A23" s="1" t="s">
+      <c r="A23" s="2" t="s">
         <v>42</v>
       </c>
       <c r="B23" t="s">
@@ -1311,7 +1300,7 @@
       </c>
     </row>
     <row r="24" spans="1:2">
-      <c r="A24" s="1" t="s">
+      <c r="A24" s="2" t="s">
         <v>44</v>
       </c>
       <c r="B24" t="s">
@@ -1319,7 +1308,7 @@
       </c>
     </row>
     <row r="25" spans="1:2">
-      <c r="A25" s="1" t="s">
+      <c r="A25" s="2" t="s">
         <v>46</v>
       </c>
       <c r="B25" t="s">
@@ -1327,232 +1316,77 @@
       </c>
     </row>
     <row r="26" spans="1:2">
-      <c r="A26" s="1"/>
+      <c r="A26" s="2"/>
     </row>
     <row r="27" spans="1:2">
-      <c r="A27" s="1"/>
+      <c r="A27" s="2"/>
     </row>
     <row r="28" spans="1:2">
-      <c r="A28" s="1"/>
+      <c r="A28" s="2"/>
     </row>
     <row r="29" spans="1:2">
-      <c r="A29" s="1"/>
+      <c r="A29" s="2"/>
     </row>
     <row r="30" spans="1:2">
-      <c r="A30" s="1"/>
+      <c r="A30" s="2"/>
     </row>
     <row r="31" spans="1:2">
-      <c r="A31" s="1"/>
+      <c r="A31" s="2"/>
     </row>
     <row r="32" spans="1:2">
-      <c r="A32" s="1"/>
+      <c r="A32" s="2"/>
     </row>
     <row r="33" spans="1:1">
-      <c r="A33" s="1"/>
+      <c r="A33" s="2"/>
     </row>
     <row r="34" spans="1:1">
-      <c r="A34" s="1"/>
+      <c r="A34" s="2"/>
     </row>
     <row r="35" spans="1:1">
-      <c r="A35" s="1"/>
+      <c r="A35" s="2"/>
     </row>
     <row r="36" spans="1:1">
-      <c r="A36" s="1"/>
+      <c r="A36" s="2"/>
     </row>
     <row r="37" spans="1:1">
-      <c r="A37" s="1"/>
+      <c r="A37" s="2"/>
     </row>
     <row r="38" spans="1:1">
-      <c r="A38" s="1"/>
+      <c r="A38" s="2"/>
     </row>
     <row r="39" spans="1:1">
-      <c r="A39" s="1"/>
+      <c r="A39" s="2"/>
     </row>
     <row r="40" spans="1:1">
-      <c r="A40" s="1"/>
+      <c r="A40" s="2"/>
     </row>
     <row r="41" spans="1:1">
-      <c r="A41" s="1"/>
+      <c r="A41" s="2"/>
     </row>
     <row r="42" spans="1:1">
-      <c r="A42" s="1"/>
+      <c r="A42" s="2"/>
     </row>
     <row r="43" spans="1:1">
-      <c r="A43" s="1"/>
+      <c r="A43" s="2"/>
     </row>
     <row r="44" spans="1:1">
-      <c r="A44" s="1"/>
+      <c r="A44" s="2"/>
     </row>
     <row r="45" spans="1:1">
-      <c r="A45" s="1"/>
+      <c r="A45" s="2"/>
     </row>
     <row r="46" spans="1:1">
-      <c r="A46" s="1"/>
+      <c r="A46" s="2"/>
     </row>
     <row r="47" spans="1:1">
-      <c r="A47" s="1"/>
+      <c r="A47" s="2"/>
     </row>
     <row r="48" spans="1:1">
-      <c r="A48" s="1"/>
+      <c r="A48" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:A26"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1">
-      <c r="A2" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1">
-      <c r="A4" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1">
-      <c r="A6" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1">
-      <c r="A7" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1">
-      <c r="A8" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1">
-      <c r="A9" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1">
-      <c r="A10" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1">
-      <c r="A11" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1">
-      <c r="A12" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1">
-      <c r="A13" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1">
-      <c r="A14" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1">
-      <c r="A15" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1">
-      <c r="A16" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1">
-      <c r="A17" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1">
-      <c r="A18" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1">
-      <c r="A19" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1">
-      <c r="A20" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1">
-      <c r="A21" s="1" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1">
-      <c r="A22" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1">
-      <c r="A23" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1">
-      <c r="A24" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1">
-      <c r="A25" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1">
-      <c r="A26" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
-</worksheet>
 </file>